--- a/artfynd/A 20926-2023 artfynd.xlsx
+++ b/artfynd/A 20926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132085597</v>
       </c>
       <c r="B2" t="n">
-        <v>97960</v>
+        <v>97963</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>132085441</v>
       </c>
       <c r="B3" t="n">
-        <v>96325</v>
+        <v>96328</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20926-2023 artfynd.xlsx
+++ b/artfynd/A 20926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132085597</v>
       </c>
       <c r="B2" t="n">
-        <v>97963</v>
+        <v>97971</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>132085441</v>
       </c>
       <c r="B3" t="n">
-        <v>96328</v>
+        <v>96336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20926-2023 artfynd.xlsx
+++ b/artfynd/A 20926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132085597</v>
       </c>
       <c r="B2" t="n">
-        <v>97971</v>
+        <v>97981</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>132085441</v>
       </c>
       <c r="B3" t="n">
-        <v>96336</v>
+        <v>96346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20926-2023 artfynd.xlsx
+++ b/artfynd/A 20926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132085597</v>
       </c>
       <c r="B2" t="n">
-        <v>97981</v>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>132085441</v>
       </c>
       <c r="B3" t="n">
-        <v>96346</v>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20926-2023 artfynd.xlsx
+++ b/artfynd/A 20926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132085597</v>
       </c>
       <c r="B2" t="n">
-        <v>97983</v>
+        <v>97984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>132085441</v>
       </c>
       <c r="B3" t="n">
-        <v>96348</v>
+        <v>96349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20926-2023 artfynd.xlsx
+++ b/artfynd/A 20926-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132085597</v>
       </c>
       <c r="B2" t="n">
-        <v>97984</v>
+        <v>97986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>132085441</v>
       </c>
       <c r="B3" t="n">
-        <v>96349</v>
+        <v>96351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20926-2023 artfynd.xlsx
+++ b/artfynd/A 20926-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132085597</v>
+        <v>132085627</v>
       </c>
       <c r="B2" t="n">
-        <v>97986</v>
+        <v>98623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220007</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Missne</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Calla palustris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>480442</v>
+        <v>480256</v>
       </c>
       <c r="R2" t="n">
-        <v>6254189</v>
+        <v>6254334</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -776,10 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132085441</v>
+        <v>132085597</v>
       </c>
       <c r="B3" t="n">
-        <v>96351</v>
+        <v>98060</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -811,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>480498</v>
+        <v>480442</v>
       </c>
       <c r="R3" t="n">
-        <v>6254340</v>
+        <v>6254189</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -870,6 +870,208 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>132085441</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96423</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2810</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Västlig hakmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus loreus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Granö, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>480498</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6254340</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Almundsryd</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering (NVI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132085890</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98219</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219815</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ekbräken</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Gymnocarpium dryopteris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Granö, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>480502</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6254359</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kronoberg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Tingsryd</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Almundsryd</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-05-20</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Maya Edlund, Gunnar Gredeby, Lars Salomon</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
         <is>
           <t>Naturvärdesinventering (NVI)</t>
         </is>

--- a/artfynd/A 20926-2023 artfynd.xlsx
+++ b/artfynd/A 20926-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085441</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085890</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085627</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,8 +1096,19 @@
           <t>Naturvärdesinventering (NVI)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132085597</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>